--- a/artfynd/A 35502-2021 artfynd.xlsx
+++ b/artfynd/A 35502-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35502-2021 artfynd.xlsx
+++ b/artfynd/A 35502-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7072639</v>
+        <v>164381</v>
       </c>
       <c r="B2" t="n">
-        <v>93323</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,20 +703,36 @@
           <t>(Hedw.) Hampe</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rosendal, V om, Hl</t>
+          <t>Nyårsåsen, Rosenberg, 350 m NO om gården, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>367182.194734456</v>
+        <v>367182</v>
       </c>
       <c r="R2" t="n">
-        <v>6290860.357651085</v>
+        <v>6290860</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,54 +756,61 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-11-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1982-09-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-11-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1982-09-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bar jord på hygge och lite i vägkant, men inget spår av arten</t>
+          <t>Mossexkursion med Jan-Erik Cederfelt, Sven-Göran Höjman, Hanna Nilsson, Erik Snygg och Sten Axel Westerström. Utgången i slutet av 1980-talet</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Vid skogsväg genom blandskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>jordhög</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Kjell Georgson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>BGM – tre mossor 2013</t>
-        </is>
-      </c>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
